--- a/reports/scan/sqlite_cbg_sqlite.xlsx
+++ b/reports/scan/sqlite_cbg_sqlite.xlsx
@@ -670,9 +670,9 @@
           <t>20</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">

--- a/reports/scan/sqlite_cbg_sqlite.xlsx
+++ b/reports/scan/sqlite_cbg_sqlite.xlsx
@@ -32,7 +32,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -41,12 +41,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00FFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00FFCC99"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFEB9C"/>
+        <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
   </fills>
@@ -62,11 +67,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -475,25 +481,25 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>16</t>
         </is>
@@ -507,27 +513,27 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>6</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>16</t>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
         </is>
       </c>
     </row>
@@ -539,27 +545,27 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>6</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>16</t>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
         </is>
       </c>
     </row>
@@ -569,27 +575,27 @@
           <t>experiments</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>12</t>
         </is>
@@ -601,27 +607,27 @@
           <t>publications</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
@@ -635,27 +641,27 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E7" s="3" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>16</t>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
         </is>
       </c>
     </row>
@@ -667,25 +673,25 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
         <is>
           <t>20</t>
         </is>
@@ -796,7 +802,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -806,7 +812,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">

--- a/reports/scan/sqlite_cbg_sqlite.xlsx
+++ b/reports/scan/sqlite_cbg_sqlite.xlsx
@@ -41,12 +41,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFEB9C"/>
+        <fgColor rgb="00FFCC99"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFCC99"/>
+        <fgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
     <fill>
@@ -481,25 +481,25 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>16</t>
         </is>
@@ -511,7 +511,7 @@
           <t>projects</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>12</t>
         </is>
@@ -521,17 +521,17 @@
           <t>6</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>12</t>
         </is>
@@ -543,7 +543,7 @@
           <t>datasets</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>12</t>
         </is>
@@ -553,17 +553,17 @@
           <t>6</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>12</t>
         </is>
@@ -575,27 +575,27 @@
           <t>experiments</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>12</t>
         </is>
@@ -607,27 +607,27 @@
           <t>publications</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E6" s="3" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F6" s="3" t="inlineStr">
         <is>
           <t>8</t>
         </is>
@@ -641,27 +641,27 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>16</t>
         </is>
       </c>
     </row>
@@ -671,27 +671,27 @@
           <t>api_keys</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>20</t>
         </is>
